--- a/kits/pdf-binder/samples/sds-binder/output/SAMPLE_SDS-Binder_Riverside-Auto-Care-index.xlsx
+++ b/kits/pdf-binder/samples/sds-binder/output/SAMPLE_SDS-Binder_Riverside-Auto-Care-index.xlsx
@@ -92,7 +92,7 @@
     <t>Bluepeak All-Season Windshield Washer Fluid -20°F</t>
   </si>
   <si>
-    <t>Bluepeak Consumer Products Co. T · Revised Feb 14, 2023</t>
+    <t>Bluepeak Consumer Products Co. · Revised Feb 14, 2023</t>
   </si>
   <si>
     <t>Included</t>
@@ -104,7 +104,7 @@
     <t>all</t>
   </si>
   <si>
-    <t>5c007a38005063bdeaff39419b036154d9a98298da2302e882ace2f8855c9e31</t>
+    <t>24c7cede1fc395071793ab7ecc6028b495c589a341b1a53564079c6276997df3</t>
   </si>
   <si>
     <t>1.2</t>
@@ -119,7 +119,7 @@
     <t>Corvane_CB-200_Brake-Parts-Cleaner_SDS_US_EN.pdf</t>
   </si>
   <si>
-    <t>402124c977795a742f6e617ca4b4616a0514f62df83937f81972d0ebdde17b0e</t>
+    <t>76f580633edaaf1a7938d759273f8a19662c53a661ace783e656c1b80ae545c3</t>
   </si>
   <si>
     <t>1.3</t>
@@ -134,7 +134,7 @@
     <t>HALBERD-RUST-PENETRANT-SDS-2019.pdf</t>
   </si>
   <si>
-    <t>1e7f8382895d5d001e93b21325ec913b461eb7b4808de6cfa2f674a94dd9d2f7</t>
+    <t>942cb13aab1628ebc27dffad1475b66d2e1c122d768bc1625475f9c2a71fcd69</t>
   </si>
   <si>
     <t>1.4</t>
@@ -143,13 +143,13 @@
     <t>Ironvale Synthetic Motor Oil 5W-30</t>
   </si>
   <si>
-    <t>Ironvale Lubricants LLC E · Revised Nov 22, 2024</t>
+    <t>Ironvale Lubricants LLC · Revised Nov 22, 2024</t>
   </si>
   <si>
     <t>ironvale-5w30-synthetic-sds.pdf</t>
   </si>
   <si>
-    <t>0207ff8262bdb8587e2af58b7db67f60be1d74c507101f9acb9174b58cf3ce9f</t>
+    <t>c801e88efd7de92abdbee07c36a9dca36933cfd529fb1350bf64f5f7558841dc</t>
   </si>
   <si>
     <t>Pending</t>
@@ -188,7 +188,7 @@
     <t>saltmarsh_primer_gray_sds.pdf</t>
   </si>
   <si>
-    <t>545044d0e87227ea787267501e61d1392b8ae0bb6415369939f2883ab9ad0927</t>
+    <t>35f2dd181df39ceffde8b13eec7186242afe793cfc4f41797dee72cacca1b24f</t>
   </si>
   <si>
     <t>3</t>
@@ -206,13 +206,13 @@
     <t>Gristmill Heavy-Duty Degreaser Concentrate</t>
   </si>
   <si>
-    <t>Gristmill Cleaning Solutions, Inc. E · Dated Aug 21, 2025</t>
+    <t>Gristmill Cleaning Solutions, Inc. · Dated Aug 21, 2025</t>
   </si>
   <si>
     <t>Gristmill-HD-Degreaser-GM-HD-5-SDS.pdf</t>
   </si>
   <si>
-    <t>3017cf090abe281107ca819944102d69b52173992ac95f7f504ad7f60f058dc5</t>
+    <t>427144d9e38457ff822c1bdb581d592d41981fc8cad1c117dfe0a5fd8eb6ddc3</t>
   </si>
   <si>
     <t>4</t>
@@ -233,7 +233,7 @@
     <t>pemberton-glass-cleaner.pdf</t>
   </si>
   <si>
-    <t>b024a46d9e0af7d2bbc4b2179337ebac599ddb63e6367eef6dccefa1d3ade069</t>
+    <t>b144d3bcea51ecb2e13817b9df06057a0669fdd47acb60582037492e538f1342</t>
   </si>
   <si>
     <t>4.2</t>
@@ -248,7 +248,7 @@
     <t>tri-county-hand-cleaner-msds.pdf</t>
   </si>
   <si>
-    <t>90ed5249eb62f425a391a6fc6d3e2b05e079d28cd52993945a6a4e3fd308b5af</t>
+    <t>fbdedf7066d1041a99e5d1d6e74b1e9176bfdeeb4af49890b7ca2604828e500d</t>
   </si>
   <si>
     <t>Binder summary</t>
@@ -269,7 +269,7 @@
     <t>Built on</t>
   </si>
   <si>
-    <t>2026-10-07 10:28</t>
+    <t>2026-10-07 10:35</t>
   </si>
   <si>
     <t>Total pages</t>
@@ -317,7 +317,7 @@
     <t>Warnings</t>
   </si>
   <si>
-    <t>1 PDF(s) in the folder are not in the index: lanternfly-tire-shine-sds.pdf</t>
+    <t>1 row(s) marked include = no were left out on purpose.</t>
   </si>
 </sst>
 </file>

--- a/kits/pdf-binder/samples/sds-binder/output/SAMPLE_SDS-Binder_Riverside-Auto-Care-index.xlsx
+++ b/kits/pdf-binder/samples/sds-binder/output/SAMPLE_SDS-Binder_Riverside-Auto-Care-index.xlsx
@@ -104,7 +104,7 @@
     <t>all</t>
   </si>
   <si>
-    <t>24c7cede1fc395071793ab7ecc6028b495c589a341b1a53564079c6276997df3</t>
+    <t>057f674dd208fa07b5bf9707c8d0d51f0b0a14b057c9d5716149f5beb412def3</t>
   </si>
   <si>
     <t>1.2</t>
@@ -119,7 +119,7 @@
     <t>Corvane_CB-200_Brake-Parts-Cleaner_SDS_US_EN.pdf</t>
   </si>
   <si>
-    <t>76f580633edaaf1a7938d759273f8a19662c53a661ace783e656c1b80ae545c3</t>
+    <t>1234df8494124e336b044ac8d0c63a84a2d96972128babdf12fda4749077f8a0</t>
   </si>
   <si>
     <t>1.3</t>
@@ -134,7 +134,7 @@
     <t>HALBERD-RUST-PENETRANT-SDS-2019.pdf</t>
   </si>
   <si>
-    <t>942cb13aab1628ebc27dffad1475b66d2e1c122d768bc1625475f9c2a71fcd69</t>
+    <t>e60c4a80c29d73f14175b725aebfce227da47b6ec3d49266dfa1f713a164bf1c</t>
   </si>
   <si>
     <t>1.4</t>
@@ -149,7 +149,7 @@
     <t>ironvale-5w30-synthetic-sds.pdf</t>
   </si>
   <si>
-    <t>c801e88efd7de92abdbee07c36a9dca36933cfd529fb1350bf64f5f7558841dc</t>
+    <t>67b56cb39fc8b6234a13c14d5ef65fbe6908d8c15c287008d47d028ccc194f48</t>
   </si>
   <si>
     <t>Pending</t>
@@ -188,7 +188,7 @@
     <t>saltmarsh_primer_gray_sds.pdf</t>
   </si>
   <si>
-    <t>35f2dd181df39ceffde8b13eec7186242afe793cfc4f41797dee72cacca1b24f</t>
+    <t>f0f79b31778dc4f75a8564355e7ef25f713565ae0d5f2bc6913cc98acf1ed91d</t>
   </si>
   <si>
     <t>3</t>
@@ -212,7 +212,7 @@
     <t>Gristmill-HD-Degreaser-GM-HD-5-SDS.pdf</t>
   </si>
   <si>
-    <t>427144d9e38457ff822c1bdb581d592d41981fc8cad1c117dfe0a5fd8eb6ddc3</t>
+    <t>e731026638145ef5c57964d629cd9b074f2770ad5abf0f8d490d306ebc989227</t>
   </si>
   <si>
     <t>4</t>
@@ -233,7 +233,7 @@
     <t>pemberton-glass-cleaner.pdf</t>
   </si>
   <si>
-    <t>b144d3bcea51ecb2e13817b9df06057a0669fdd47acb60582037492e538f1342</t>
+    <t>fe9523f3a3ea661370159bcb776b4318eacfcd4b3276e8a754137f74c1735697</t>
   </si>
   <si>
     <t>4.2</t>
@@ -248,7 +248,7 @@
     <t>tri-county-hand-cleaner-msds.pdf</t>
   </si>
   <si>
-    <t>fbdedf7066d1041a99e5d1d6e74b1e9176bfdeeb4af49890b7ca2604828e500d</t>
+    <t>bb854172ad5bda1e374c410e5e9e25688992e3ff138efec73127986338c65d1f</t>
   </si>
   <si>
     <t>Binder summary</t>
@@ -269,7 +269,7 @@
     <t>Built on</t>
   </si>
   <si>
-    <t>2026-10-07 10:35</t>
+    <t>2026-10-07 10:36</t>
   </si>
   <si>
     <t>Total pages</t>

--- a/kits/pdf-binder/samples/sds-binder/output/SAMPLE_SDS-Binder_Riverside-Auto-Care-index.xlsx
+++ b/kits/pdf-binder/samples/sds-binder/output/SAMPLE_SDS-Binder_Riverside-Auto-Care-index.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="101">
   <si>
     <t>Type</t>
   </si>
@@ -104,7 +104,7 @@
     <t>all</t>
   </si>
   <si>
-    <t>057f674dd208fa07b5bf9707c8d0d51f0b0a14b057c9d5716149f5beb412def3</t>
+    <t>a2f5c09c0ea46b3998dfe68286e48a5c94bfc869b53c65beeb7811824e71177f</t>
   </si>
   <si>
     <t>1.2</t>
@@ -119,7 +119,7 @@
     <t>Corvane_CB-200_Brake-Parts-Cleaner_SDS_US_EN.pdf</t>
   </si>
   <si>
-    <t>1234df8494124e336b044ac8d0c63a84a2d96972128babdf12fda4749077f8a0</t>
+    <t>b7e8850d95dff694592fc06c263946fd8dba8f259489039db9245dcd86c6a0ba</t>
   </si>
   <si>
     <t>1.3</t>
@@ -134,7 +134,7 @@
     <t>HALBERD-RUST-PENETRANT-SDS-2019.pdf</t>
   </si>
   <si>
-    <t>e60c4a80c29d73f14175b725aebfce227da47b6ec3d49266dfa1f713a164bf1c</t>
+    <t>3be26f159661130cac2a3fe19d6b3cdcaa77633f4bfa392e38176d7af6c81207</t>
   </si>
   <si>
     <t>1.4</t>
@@ -149,7 +149,7 @@
     <t>ironvale-5w30-synthetic-sds.pdf</t>
   </si>
   <si>
-    <t>67b56cb39fc8b6234a13c14d5ef65fbe6908d8c15c287008d47d028ccc194f48</t>
+    <t>b8bac6b3014389a48d92c80e0c30c67fcb15caabbd05f7e0f1c44267381664b1</t>
   </si>
   <si>
     <t>Pending</t>
@@ -188,7 +188,7 @@
     <t>saltmarsh_primer_gray_sds.pdf</t>
   </si>
   <si>
-    <t>f0f79b31778dc4f75a8564355e7ef25f713565ae0d5f2bc6913cc98acf1ed91d</t>
+    <t>f30a6760f3ba99932a0e2c17305cbce4a28d692ed02b0d86afc88d1850c5161c</t>
   </si>
   <si>
     <t>3</t>
@@ -212,7 +212,7 @@
     <t>Gristmill-HD-Degreaser-GM-HD-5-SDS.pdf</t>
   </si>
   <si>
-    <t>e731026638145ef5c57964d629cd9b074f2770ad5abf0f8d490d306ebc989227</t>
+    <t>32e485c29e356ecccdbb0087dcfde63b54ee09dc5dae076c628fa591c1834cd1</t>
   </si>
   <si>
     <t>4</t>
@@ -230,10 +230,13 @@
     <t>Pemberton Glass Cleaner</t>
   </si>
   <si>
+    <t>Pemberton Household Supply (fictional) · Revised Sep 3, 2024</t>
+  </si>
+  <si>
     <t>pemberton-glass-cleaner.pdf</t>
   </si>
   <si>
-    <t>fe9523f3a3ea661370159bcb776b4318eacfcd4b3276e8a754137f74c1735697</t>
+    <t>6e324332016a601d99ede6c9eeb61a54468f5843c1d87a08fe470c06b31ad161</t>
   </si>
   <si>
     <t>4.2</t>
@@ -248,7 +251,7 @@
     <t>tri-county-hand-cleaner-msds.pdf</t>
   </si>
   <si>
-    <t>bb854172ad5bda1e374c410e5e9e25688992e3ff138efec73127986338c65d1f</t>
+    <t>f2d38657c97ec83f71a1243ebc96fc1d4018add990b3b084e4624ccc089448a9</t>
   </si>
   <si>
     <t>Binder summary</t>
@@ -269,7 +272,7 @@
     <t>Built on</t>
   </si>
   <si>
-    <t>2026-10-07 10:36</t>
+    <t>2026-10-07 10:49</t>
   </si>
   <si>
     <t>Total pages</t>
@@ -1293,12 +1296,14 @@
       <c r="E15" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F15" s="2"/>
+      <c r="F15" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="G15" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>27</v>
@@ -1313,7 +1318,7 @@
         <v>23</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1327,19 +1332,19 @@
         <v>66</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>27</v>
@@ -1354,7 +1359,7 @@
         <v>24</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1379,15 +1384,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1395,28 +1400,28 @@
         <v>4</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B7" s="8">
         <v>24</v>
@@ -1424,7 +1429,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B8" s="8">
         <v>4</v>
@@ -1432,7 +1437,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B9" s="8">
         <v>8</v>
@@ -1440,7 +1445,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B10" s="8">
         <v>1</v>
@@ -1448,7 +1453,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B11" s="8">
         <v>1</v>
@@ -1456,7 +1461,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B12" s="8">
         <v>4</v>
@@ -1464,42 +1469,42 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
